--- a/Network_demand_scenario_input.xlsx
+++ b/Network_demand_scenario_input.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Total_Cost" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fill_Rate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total_Cost" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fill_Rate" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -532,124 +532,159 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mean Fill Rate (%) per (Instance × Scenario × Model). GREEN cells are pre-filled</t>
+          <t>mean Fill Rate (%) per (Network x Scenario x Model).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>from evaluation_results/robustness_comparison/robustness_summary.csv (2x15 only).</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sheets:</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sheets:</t>
+          <t xml:space="preserve">  Total_Cost  — values in raw VND (the chart script divides by 1000).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Total_Cost  — values in raw VND (the plotting script divides by 1000).</t>
+          <t xml:space="preserve">  Fill_Rate   — values in % (0-100).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Fill_Rate   — values in % (0–100).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Scenarios:</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scenarios:</t>
+          <t xml:space="preserve">  S1-Balanced  — low-stress, matches training distribution</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • S1-Balanced  — low-stress, matches training distribution</t>
+          <t xml:space="preserve">  S2-High      — elevated demand means, mixed stress</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • S2-High      — elevated demand means, mixed stress</t>
+          <t xml:space="preserve">  S3-Extreme   — original means + high volatility</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • S3-Extreme   — original means + high volatility</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Networks (10 topologies):</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Instances:</t>
+          <t xml:space="preserve">  Network 1 (1x3)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Instance 1 (1x7)   — 1 DC × 7 retailers</t>
+          <t xml:space="preserve">  Network 2 (1x7)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Instance 2 (2x15)  — 2 DCs × 15 retailers (thesis base, pre-filled)</t>
+          <t xml:space="preserve">  Network 3 (1x10)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Instance 3 (2x30)  — 2 DCs × 30 retailers</t>
+          <t xml:space="preserve">  Network 4 (2x15)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Instance 4 (4x40)  — 4 DCs × 40 retailers</t>
+          <t xml:space="preserve">  Network 5 (2x20)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Network 6 (2x30)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Once filled, run:  python Network_demand_scenario.py</t>
+          <t xml:space="preserve">  Network 7 (2x40)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Outputs: total_cost_comparison.png and fill_rate_comparison.png</t>
+          <t xml:space="preserve">  Network 8 (4x15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Network 9 (4x30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Network 10 (4x40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Once filled, run:  python Network_demand_vechart.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Outputs: NetworkDemand_cost_comparison.png, NetworkDemand_fill_rate_comparison.png</t>
         </is>
       </c>
     </row>
@@ -664,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -716,12 +751,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Instance 1</t>
+          <t>Network 1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1x7</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -763,12 +798,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Instance 2</t>
+          <t>Network 2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>1x7</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -776,18 +811,10 @@
           <t>S1-Balanced</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>160131.56</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>139066.56</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>178039.58</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>258222.03</v>
-      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -797,18 +824,10 @@
           <t>S2-High</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>257726.45</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>181568.49</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>221956.07</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>263903.67</v>
-      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -818,28 +837,20 @@
           <t>S3-Extreme</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>194440.45</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>145274.33</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>174133.29</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>254368.38</v>
-      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Instance 3</t>
+          <t>Network 3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2x30</t>
+          <t>1x10</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -881,12 +892,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Instance 4</t>
+          <t>Network 4</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4x40</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -894,10 +905,18 @@
           <t>S1-Balanced</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="D11" s="7" t="n">
+        <v>160131.56</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>139066.56</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>178039.58</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>258222.03</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -907,10 +926,18 @@
           <t>S2-High</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="D12" s="7" t="n">
+        <v>257726.45</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>181568.49</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>221956.07</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>263903.67</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -920,21 +947,323 @@
           <t>S3-Extreme</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="D13" s="7" t="n">
+        <v>194440.45</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>145274.33</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>174133.29</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>254368.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Network 5</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Network 6</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2x30</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Network 7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2x40</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Network 8</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>4x15</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Network 9</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>4x30</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Network 10</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>4x40</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="20">
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
     <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B29:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -946,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -998,12 +1327,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Instance 1</t>
+          <t>Network 1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1x7</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1045,12 +1374,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Instance 2</t>
+          <t>Network 2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2x15</t>
+          <t>1x7</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1058,18 +1387,10 @@
           <t>S1-Balanced</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>93.67</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>79.23999999999999</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>77.18000000000001</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>94.66</v>
-      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1079,18 +1400,10 @@
           <t>S2-High</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>89.45999999999999</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>69.87</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>84.39</v>
-      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -1100,28 +1413,20 @@
           <t>S3-Extreme</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>91.86</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>74.68000000000001</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>93.76000000000001</v>
-      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Instance 3</t>
+          <t>Network 3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2x30</t>
+          <t>1x10</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1163,12 +1468,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Instance 4</t>
+          <t>Network 4</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4x40</t>
+          <t>2x15</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1176,10 +1481,18 @@
           <t>S1-Balanced</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="D11" s="9" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>94.66</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1189,10 +1502,18 @@
           <t>S2-High</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="D12" s="9" t="n">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>84.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1202,21 +1523,323 @@
           <t>S3-Extreme</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="D13" s="9" t="n">
+        <v>91.86</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>93.76000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Network 5</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2x20</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Network 6</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2x30</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Network 7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2x40</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Network 8</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>4x15</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Network 9</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>4x30</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Network 10</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>4x40</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>S1-Balanced</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>S2-High</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>S3-Extreme</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="20">
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A26:A28"/>
     <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B29:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
